--- a/config/platforms.xlsx
+++ b/config/platforms.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t xml:space="preserve">Платформа</t>
   </si>
@@ -40,82 +40,98 @@
     <t xml:space="preserve">avito.ru</t>
   </si>
   <si>
+    <t xml:space="preserve">sutochno.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Otello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отелло</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1001Kvartira.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bronevik.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cian.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kvartirka.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ostrovok.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tvil.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">жилибыли</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Яндекс Путешествия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Постоянный гость</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Модуль бронирования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ДомКлик24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bookings_widget@tutt.ru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">basket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корзина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YandexTravel</t>
+  </si>
+  <si>
     <t xml:space="preserve">17.0</t>
   </si>
   <si>
-    <t xml:space="preserve">sutochno.ru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Otello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1001Kvartira.ru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bronevik.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cian.ru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kvartirka.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ostrovok.ru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tvil.ru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">жилибыли</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Яндекс Путешествия</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Постоянный гость</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Модуль бронирования</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ДомКлик24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bookings_widget@tutt.ru</t>
-  </si>
-  <si>
-    <t xml:space="preserve">basket</t>
+    <t xml:space="preserve">DomClick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cian</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="dd/mmm"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -192,7 +208,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -202,6 +218,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -332,14 +352,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="11.5625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="21.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="21.44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -350,7 +370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -358,132 +378,172 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="17" customFormat="false" ht="13" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C16" r:id="rId1" display="bookings_widget@tutt.ru"/>
+    <hyperlink ref="C17" r:id="rId1" display="bookings_widget@tutt.ru"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
